--- a/results/reporte_hpc.xlsx
+++ b/results/reporte_hpc.xlsx
@@ -8,8 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Secuencial" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gráficas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2 Hilos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="4 Hilos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6 Hilos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="8 Hilos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="12 Hilos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Procesos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Resumen" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gráficas" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -309,12 +315,204 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Gráficas'!$A$3:$A$9</f>
+              <f>'Gráficas'!$A$3:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficas'!$B$3:$B$9</f>
+              <f>'Gráficas'!$B$3:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!C2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$C$3:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!D2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$D$3:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!E2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$E$3:$E$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!F2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$F$3:$F$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!G2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$G$3:$G$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!H2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$H$3:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -405,6 +603,198 @@
     <plotArea>
       <lineChart>
         <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!C10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$11:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$C$11:$C$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!D10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$11:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$D$11:$D$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!E10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$11:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$E$11:$E$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!F10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$11:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$F$11:$F$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!G10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$11:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$G$11:$G$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Gráficas'!H10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Gráficas'!$A$11:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Gráficas'!$H$11:$H$15</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -808,7 +1198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -903,7 +1293,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10 x 10</t>
+          <t>400 x 400</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -927,7 +1317,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>100 x 100</t>
+          <t>800 x 800</t>
         </is>
       </c>
       <c r="B4" s="8" t="n"/>
@@ -951,7 +1341,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>200 x 200</t>
+          <t>1600 x 1600</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -975,7 +1365,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>400 x 400</t>
+          <t>3200 x 3200</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -999,7 +1389,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>800 x 800</t>
+          <t>6400 x 6400</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
@@ -1017,54 +1407,6 @@
         <v/>
       </c>
       <c r="M7" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>1600 x 1600</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="6">
-        <f>AVERAGE(B8:K8)</f>
-        <v/>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>3200 x 3200</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="6">
-        <f>AVERAGE(B9:K9)</f>
-        <v/>
-      </c>
-      <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1082,148 +1424,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Resumen comparativo  |  Multiplicación de Matrices HPC</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+          <t>Multiplicación de Matrices  |  2 Hilos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Dimensión (N)</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Secuencial
-Promedio (ms)</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Secuencial
-Speedup</t>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 2</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 3</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 4</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 5</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 6</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 7</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 8</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 9</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Speedup</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10 x 10</t>
-        </is>
-      </c>
-      <c r="B3" s="5">
-        <f>IFERROR('Secuencial'!L3, "N/D")</f>
-        <v/>
-      </c>
-      <c r="C3" s="11">
-        <f>IFERROR('Secuencial'!M3, "N/D")</f>
-        <v/>
+          <t>400 x 400</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>10.424</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>10.834</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>10.537</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>10.507</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>10.496</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>10.503</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>10.538</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>10.513</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>10.658</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>10.657</v>
+      </c>
+      <c r="L3" s="6">
+        <f>AVERAGE(B3:K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>100 x 100</t>
-        </is>
-      </c>
-      <c r="B4" s="8">
-        <f>IFERROR('Secuencial'!L4, "N/D")</f>
-        <v/>
-      </c>
-      <c r="C4" s="12">
-        <f>IFERROR('Secuencial'!M4, "N/D")</f>
-        <v/>
+          <t>800 x 800</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>83.572</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>85.258</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>83.687</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>83.718</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>85.16500000000001</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>83.623</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>83.54900000000001</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>83.81699999999999</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>85.242</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>83.834</v>
+      </c>
+      <c r="L4" s="6">
+        <f>AVERAGE(B4:K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>200 x 200</t>
-        </is>
-      </c>
-      <c r="B5" s="5">
-        <f>IFERROR('Secuencial'!L5, "N/D")</f>
-        <v/>
-      </c>
-      <c r="C5" s="11">
-        <f>IFERROR('Secuencial'!M5, "N/D")</f>
-        <v/>
+          <t>1600 x 1600</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>672.905</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>680.029</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>678.083</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>666.271</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>677.674</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>678.429</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>677.794</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>665.971</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>665.947</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>665.9450000000001</v>
+      </c>
+      <c r="L5" s="6">
+        <f>AVERAGE(B5:K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>400 x 400</t>
-        </is>
-      </c>
-      <c r="B6" s="8">
-        <f>IFERROR('Secuencial'!L6, "N/D")</f>
-        <v/>
-      </c>
-      <c r="C6" s="12">
-        <f>IFERROR('Secuencial'!M6, "N/D")</f>
-        <v/>
+          <t>3200 x 3200</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>5394.507</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>5396.992</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>5394.368</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>5396.347</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>5389.872</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>5571.875</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>5573.116</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>5571.215</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>5396.298</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>5392.705</v>
+      </c>
+      <c r="L6" s="6">
+        <f>AVERAGE(B6:K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>800 x 800</t>
-        </is>
-      </c>
-      <c r="B7" s="5">
-        <f>IFERROR('Secuencial'!L7, "N/D")</f>
-        <v/>
-      </c>
-      <c r="C7" s="11">
-        <f>IFERROR('Secuencial'!M7, "N/D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>1600 x 1600</t>
-        </is>
-      </c>
-      <c r="B8" s="8">
-        <f>IFERROR('Secuencial'!L8, "N/D")</f>
-        <v/>
-      </c>
-      <c r="C8" s="12">
-        <f>IFERROR('Secuencial'!M8, "N/D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>3200 x 3200</t>
-        </is>
-      </c>
-      <c r="B9" s="5">
-        <f>IFERROR('Secuencial'!L9, "N/D")</f>
-        <v/>
-      </c>
-      <c r="C9" s="11">
-        <f>IFERROR('Secuencial'!M9, "N/D")</f>
-        <v/>
+          <t>6400 x 6400</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>50653.278</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>50537.935</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>50996.548</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>51110.168</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>51379.869</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>51465.041</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>50651.81</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>51094.009</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>51356.119</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>51299.363</v>
+      </c>
+      <c r="L7" s="6">
+        <f>AVERAGE(B7:K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1235,7 +1760,2134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Multiplicación de Matrices  |  4 Hilos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dimensión (N)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 2</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 3</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 4</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 5</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 6</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 7</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 8</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 9</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>400 x 400</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>5.396</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>5.468</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>5.421</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>5.259</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>5.407</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>5.247</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>5.271</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>5.512</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>5.394</v>
+      </c>
+      <c r="L3" s="6">
+        <f>AVERAGE(B3:K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>800 x 800</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>42.212</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>42.756</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>42.614</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>41.866</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>42.093</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>41.801</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>41.899</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>42.383</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>42.736</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>41.893</v>
+      </c>
+      <c r="L4" s="6">
+        <f>AVERAGE(B4:K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1600 x 1600</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>337.15</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>332.678</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>338.871</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>336.222</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>339.04</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>339.102</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>338.59</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>336.089</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>338.941</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>338.513</v>
+      </c>
+      <c r="L5" s="6">
+        <f>AVERAGE(B5:K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3200 x 3200</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>2756.375</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>2684.698</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>2756.906</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>2742.937</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>2750.635</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>2758.239</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>2756.61</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>2749.697</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>2756.923</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>2746.566</v>
+      </c>
+      <c r="L6" s="6">
+        <f>AVERAGE(B6:K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>6400 x 6400</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>25028.741</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>25050.99</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>25040.951</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>25001.977</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>25043.091</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>25052.906</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>24997.819</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>25022.289</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>25033.222</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>25034.074</v>
+      </c>
+      <c r="L7" s="6">
+        <f>AVERAGE(B7:K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Multiplicación de Matrices  |  6 Hilos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dimensión (N)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 2</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 3</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 4</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 5</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 6</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 7</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 8</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 9</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>400 x 400</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>3.749</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3.728</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>3.893</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>3.745</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>3.741</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>3.739</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>3.737</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>7.237</v>
+      </c>
+      <c r="L3" s="6">
+        <f>AVERAGE(B3:K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>800 x 800</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>28.261</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>28.432</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>28.453</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>28.516</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>28.531</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>28.468</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>28.519</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>28.402</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>28.494</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>28.583</v>
+      </c>
+      <c r="L4" s="6">
+        <f>AVERAGE(B4:K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1600 x 1600</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>224.853</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>224.661</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>224.738</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>226.309</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>229.12</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>225.874</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>225.475</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>225.51</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>229.026</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>225.458</v>
+      </c>
+      <c r="L5" s="6">
+        <f>AVERAGE(B5:K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3200 x 3200</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>1843.925</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1843.261</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1843.075</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1839.793</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1827.554</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1843.078</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1866.88</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>1888.741</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>1842.038</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>1846.854</v>
+      </c>
+      <c r="L6" s="6">
+        <f>AVERAGE(B6:K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>6400 x 6400</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>17110.036</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>17066.879</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>17134.161</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>17056.114</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>16891.73</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>16914.49</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>17101.799</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>16846.873</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>16979.873</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>17097.149</v>
+      </c>
+      <c r="L7" s="6">
+        <f>AVERAGE(B7:K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Multiplicación de Matrices  |  8 Hilos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dimensión (N)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 2</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 3</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 4</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 5</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 6</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 7</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 8</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 9</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>400 x 400</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>5.252</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>5.263</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>5.409</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>5.361</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>5.276</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>5.269</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>5.279</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>5.264</v>
+      </c>
+      <c r="L3" s="6">
+        <f>AVERAGE(B3:K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>800 x 800</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>41.802</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>41.837</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>41.811</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>41.816</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>41.833</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>41.857</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>41.917</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>41.806</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>42.032</v>
+      </c>
+      <c r="L4" s="6">
+        <f>AVERAGE(B4:K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1600 x 1600</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>333.056</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>332.768</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>332.59</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>332.727</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>332.834</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>332.717</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>332.776</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>332.669</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>332.622</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>332.629</v>
+      </c>
+      <c r="L5" s="6">
+        <f>AVERAGE(B5:K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3200 x 3200</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>2689.3</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>2690.99</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>2688.088</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>2688.628</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>2688.581</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>2688.191</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>2692.747</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>2690.613</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>2689.313</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>2688.137</v>
+      </c>
+      <c r="L6" s="6">
+        <f>AVERAGE(B6:K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>6400 x 6400</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>25544.36</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>25442.366</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>25163.727</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>25212.577</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>25226.005</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>25217.182</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>25165.797</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>25186.547</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>25187.951</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>25191.988</v>
+      </c>
+      <c r="L7" s="6">
+        <f>AVERAGE(B7:K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Multiplicación de Matrices  |  12 Hilos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dimensión (N)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 2</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 3</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 4</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 5</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 6</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 7</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 8</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 9</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>400 x 400</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3.816</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>3.831</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>3.847</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>4.794</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>3.869</v>
+      </c>
+      <c r="L3" s="6">
+        <f>AVERAGE(B3:K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>800 x 800</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>29.727</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>29.615</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>29.495</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>29.495</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>29.521</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>29.587</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>29.563</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>29.489</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>29.781</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>29.674</v>
+      </c>
+      <c r="L4" s="6">
+        <f>AVERAGE(B4:K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1600 x 1600</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>226.261</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>226.569</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>226.579</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>226.852</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>226.416</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>226.289</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>227.019</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>226.394</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>226.329</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>226.376</v>
+      </c>
+      <c r="L5" s="6">
+        <f>AVERAGE(B5:K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3200 x 3200</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>1842.968</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1835.944</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1841.664</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1841.887</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1840.859</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1838.709</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1835.813</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>1885.088</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>1861.609</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>1845.701</v>
+      </c>
+      <c r="L6" s="6">
+        <f>AVERAGE(B6:K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>6400 x 6400</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>17092.105</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>17022.115</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>17201.725</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>16885.791</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>17080.643</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>16948.101</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>17067.447</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>16919.753</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>16993.182</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>16873.415</v>
+      </c>
+      <c r="L7" s="6">
+        <f>AVERAGE(B7:K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Multiplicación de Matrices  |  Procesos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dimensión (N)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 2</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 3</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 4</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 5</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 6</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 7</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 8</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 9</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rep 10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>400 x 400</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>4.076</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>4.064</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>4.096</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>4.052</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>4.077</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>4.258</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>4.081</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>4.446</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L3" s="6">
+        <f>AVERAGE(B3:K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>800 x 800</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>29.821</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>29.358</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>29.347</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>29.828</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>29.143</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>29.381</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>29.927</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>29.365</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>29.371</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>29.302</v>
+      </c>
+      <c r="L4" s="6">
+        <f>AVERAGE(B4:K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1600 x 1600</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>227.752</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>227.242</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>228.041</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>229.653</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>227.62</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>227.796</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>227.519</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>227.524</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>227.419</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>227.299</v>
+      </c>
+      <c r="L5" s="6">
+        <f>AVERAGE(B5:K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3200 x 3200</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>1906.286</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1858.34</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1851.641</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1852.619</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1866.731</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1864.661</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1854.427</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>1851.568</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>1857.853</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>1900.394</v>
+      </c>
+      <c r="L6" s="6">
+        <f>AVERAGE(B6:K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>6400 x 6400</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>17179.518</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>17128.94</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>17206.619</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>17126.883</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>17169.981</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>17152.056</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>17120.707</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>17274.756</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>17171.157</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>17056.423</v>
+      </c>
+      <c r="L7" s="6">
+        <f>AVERAGE(B7:K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Sin datos seq.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Resumen comparativo  |  Multiplicación de Matrices HPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Dimensión (N)</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Secuencial
+Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Secuencial
+Speedup</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>2 Hilos
+Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>2 Hilos
+Speedup</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>4 Hilos
+Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>4 Hilos
+Speedup</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>6 Hilos
+Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>6 Hilos
+Speedup</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>8 Hilos
+Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>8 Hilos
+Speedup</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>12 Hilos
+Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>12 Hilos
+Speedup</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>Procesos
+Promedio (ms)</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>Procesos
+Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>400 x 400</t>
+        </is>
+      </c>
+      <c r="B3" s="5">
+        <f>IFERROR('Secuencial'!L3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="C3" s="11">
+        <f>IFERROR('Secuencial'!M3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="D3" s="5">
+        <f>IFERROR('2 Hilos'!L3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="E3" s="11">
+        <f>IFERROR('2 Hilos'!M3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="F3" s="5">
+        <f>IFERROR('4 Hilos'!L3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="G3" s="11">
+        <f>IFERROR('4 Hilos'!M3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="H3" s="5">
+        <f>IFERROR('6 Hilos'!L3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="I3" s="11">
+        <f>IFERROR('6 Hilos'!M3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="J3" s="5">
+        <f>IFERROR('8 Hilos'!L3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="K3" s="11">
+        <f>IFERROR('8 Hilos'!M3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="L3" s="5">
+        <f>IFERROR('12 Hilos'!L3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="M3" s="11">
+        <f>IFERROR('12 Hilos'!M3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="N3" s="5">
+        <f>IFERROR('Procesos'!L3, "N/D")</f>
+        <v/>
+      </c>
+      <c r="O3" s="11">
+        <f>IFERROR('Procesos'!M3, "N/D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>800 x 800</t>
+        </is>
+      </c>
+      <c r="B4" s="8">
+        <f>IFERROR('Secuencial'!L4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="C4" s="12">
+        <f>IFERROR('Secuencial'!M4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="D4" s="8">
+        <f>IFERROR('2 Hilos'!L4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="E4" s="12">
+        <f>IFERROR('2 Hilos'!M4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="F4" s="8">
+        <f>IFERROR('4 Hilos'!L4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="G4" s="12">
+        <f>IFERROR('4 Hilos'!M4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="H4" s="8">
+        <f>IFERROR('6 Hilos'!L4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="I4" s="12">
+        <f>IFERROR('6 Hilos'!M4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="J4" s="8">
+        <f>IFERROR('8 Hilos'!L4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="K4" s="12">
+        <f>IFERROR('8 Hilos'!M4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="L4" s="8">
+        <f>IFERROR('12 Hilos'!L4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="M4" s="12">
+        <f>IFERROR('12 Hilos'!M4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="N4" s="8">
+        <f>IFERROR('Procesos'!L4, "N/D")</f>
+        <v/>
+      </c>
+      <c r="O4" s="12">
+        <f>IFERROR('Procesos'!M4, "N/D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1600 x 1600</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>IFERROR('Secuencial'!L5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="C5" s="11">
+        <f>IFERROR('Secuencial'!M5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>IFERROR('2 Hilos'!L5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="E5" s="11">
+        <f>IFERROR('2 Hilos'!M5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="F5" s="5">
+        <f>IFERROR('4 Hilos'!L5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="G5" s="11">
+        <f>IFERROR('4 Hilos'!M5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="H5" s="5">
+        <f>IFERROR('6 Hilos'!L5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="I5" s="11">
+        <f>IFERROR('6 Hilos'!M5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="J5" s="5">
+        <f>IFERROR('8 Hilos'!L5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="K5" s="11">
+        <f>IFERROR('8 Hilos'!M5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="L5" s="5">
+        <f>IFERROR('12 Hilos'!L5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="M5" s="11">
+        <f>IFERROR('12 Hilos'!M5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="N5" s="5">
+        <f>IFERROR('Procesos'!L5, "N/D")</f>
+        <v/>
+      </c>
+      <c r="O5" s="11">
+        <f>IFERROR('Procesos'!M5, "N/D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3200 x 3200</t>
+        </is>
+      </c>
+      <c r="B6" s="8">
+        <f>IFERROR('Secuencial'!L6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="C6" s="12">
+        <f>IFERROR('Secuencial'!M6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="D6" s="8">
+        <f>IFERROR('2 Hilos'!L6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>IFERROR('2 Hilos'!M6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>IFERROR('4 Hilos'!L6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>IFERROR('4 Hilos'!M6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>IFERROR('6 Hilos'!L6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="I6" s="12">
+        <f>IFERROR('6 Hilos'!M6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="J6" s="8">
+        <f>IFERROR('8 Hilos'!L6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>IFERROR('8 Hilos'!M6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="L6" s="8">
+        <f>IFERROR('12 Hilos'!L6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="M6" s="12">
+        <f>IFERROR('12 Hilos'!M6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="N6" s="8">
+        <f>IFERROR('Procesos'!L6, "N/D")</f>
+        <v/>
+      </c>
+      <c r="O6" s="12">
+        <f>IFERROR('Procesos'!M6, "N/D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>6400 x 6400</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>IFERROR('Secuencial'!L7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>IFERROR('Secuencial'!M7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="D7" s="5">
+        <f>IFERROR('2 Hilos'!L7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>IFERROR('2 Hilos'!M7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>IFERROR('4 Hilos'!L7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="G7" s="11">
+        <f>IFERROR('4 Hilos'!M7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>IFERROR('6 Hilos'!L7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="I7" s="11">
+        <f>IFERROR('6 Hilos'!M7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>IFERROR('8 Hilos'!L7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="K7" s="11">
+        <f>IFERROR('8 Hilos'!M7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>IFERROR('12 Hilos'!L7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="M7" s="11">
+        <f>IFERROR('12 Hilos'!M7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="N7" s="5">
+        <f>IFERROR('Procesos'!L7, "N/D")</f>
+        <v/>
+      </c>
+      <c r="O7" s="11">
+        <f>IFERROR('Procesos'!M7, "N/D")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,137 +3908,401 @@
           <t>Secuencial</t>
         </is>
       </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>2 Hilos</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>4 Hilos</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>6 Hilos</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>8 Hilos</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>12 Hilos</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Procesos</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="B3">
         <f>IFERROR(Resumen!B3, 0)</f>
         <v/>
       </c>
+      <c r="C3">
+        <f>IFERROR(Resumen!D3, 0)</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>IFERROR(Resumen!F3, 0)</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>IFERROR(Resumen!H3, 0)</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>IFERROR(Resumen!J3, 0)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>IFERROR(Resumen!L3, 0)</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>IFERROR(Resumen!N3, 0)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="B4">
         <f>IFERROR(Resumen!B4, 0)</f>
         <v/>
       </c>
+      <c r="C4">
+        <f>IFERROR(Resumen!D4, 0)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>IFERROR(Resumen!F4, 0)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>IFERROR(Resumen!H4, 0)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>IFERROR(Resumen!J4, 0)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>IFERROR(Resumen!L4, 0)</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>IFERROR(Resumen!N4, 0)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="B5">
         <f>IFERROR(Resumen!B5, 0)</f>
         <v/>
       </c>
+      <c r="C5">
+        <f>IFERROR(Resumen!D5, 0)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>IFERROR(Resumen!F5, 0)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>IFERROR(Resumen!H5, 0)</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>IFERROR(Resumen!J5, 0)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IFERROR(Resumen!L5, 0)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>IFERROR(Resumen!N5, 0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>400</v>
+        <v>3200</v>
       </c>
       <c r="B6">
         <f>IFERROR(Resumen!B6, 0)</f>
         <v/>
       </c>
+      <c r="C6">
+        <f>IFERROR(Resumen!D6, 0)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>IFERROR(Resumen!F6, 0)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>IFERROR(Resumen!H6, 0)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>IFERROR(Resumen!J6, 0)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IFERROR(Resumen!L6, 0)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>IFERROR(Resumen!N6, 0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>800</v>
+        <v>6400</v>
       </c>
       <c r="B7">
         <f>IFERROR(Resumen!B7, 0)</f>
         <v/>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1600</v>
-      </c>
-      <c r="B8">
-        <f>IFERROR(Resumen!B8, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3200</v>
-      </c>
-      <c r="B9">
-        <f>IFERROR(Resumen!B9, 0)</f>
+      <c r="C7">
+        <f>IFERROR(Resumen!D7, 0)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>IFERROR(Resumen!F7, 0)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>IFERROR(Resumen!H7, 0)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>IFERROR(Resumen!J7, 0)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IFERROR(Resumen!L7, 0)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>IFERROR(Resumen!N7, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Dimensión</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>2 Hilos</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>4 Hilos</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>6 Hilos</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>8 Hilos</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>12 Hilos</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Procesos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>400</v>
+      </c>
+      <c r="B11">
+        <f>IFERROR(Resumen!C3, 0)</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>IFERROR(Resumen!E3, 0)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>IFERROR(Resumen!G3, 0)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>IFERROR(Resumen!I3, 0)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>IFERROR(Resumen!K3, 0)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>IFERROR(Resumen!M3, 0)</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>IFERROR(Resumen!O3, 0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Dimensión</t>
-        </is>
+      <c r="A12" t="n">
+        <v>800</v>
+      </c>
+      <c r="B12">
+        <f>IFERROR(Resumen!C4, 0)</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>IFERROR(Resumen!E4, 0)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>IFERROR(Resumen!G4, 0)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>IFERROR(Resumen!I4, 0)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>IFERROR(Resumen!K4, 0)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IFERROR(Resumen!M4, 0)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>IFERROR(Resumen!O4, 0)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>1600</v>
       </c>
       <c r="B13">
-        <f>IFERROR(Resumen!C3, 0)</f>
+        <f>IFERROR(Resumen!C5, 0)</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>IFERROR(Resumen!E5, 0)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>IFERROR(Resumen!G5, 0)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>IFERROR(Resumen!I5, 0)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>IFERROR(Resumen!K5, 0)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>IFERROR(Resumen!M5, 0)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>IFERROR(Resumen!O5, 0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100</v>
+        <v>3200</v>
       </c>
       <c r="B14">
-        <f>IFERROR(Resumen!C4, 0)</f>
+        <f>IFERROR(Resumen!C6, 0)</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>IFERROR(Resumen!E6, 0)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>IFERROR(Resumen!G6, 0)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>IFERROR(Resumen!I6, 0)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>IFERROR(Resumen!K6, 0)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>IFERROR(Resumen!M6, 0)</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>IFERROR(Resumen!O6, 0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>200</v>
+        <v>6400</v>
       </c>
       <c r="B15">
-        <f>IFERROR(Resumen!C5, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>400</v>
-      </c>
-      <c r="B16">
-        <f>IFERROR(Resumen!C6, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>800</v>
-      </c>
-      <c r="B17">
         <f>IFERROR(Resumen!C7, 0)</f>
         <v/>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1600</v>
-      </c>
-      <c r="B18">
-        <f>IFERROR(Resumen!C8, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>3200</v>
-      </c>
-      <c r="B19">
-        <f>IFERROR(Resumen!C9, 0)</f>
+      <c r="C15">
+        <f>IFERROR(Resumen!E7, 0)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>IFERROR(Resumen!G7, 0)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>IFERROR(Resumen!I7, 0)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>IFERROR(Resumen!K7, 0)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>IFERROR(Resumen!M7, 0)</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>IFERROR(Resumen!O7, 0)</f>
         <v/>
       </c>
     </row>

--- a/results/reporte_hpc.xlsx
+++ b/results/reporte_hpc.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sequential" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Threads" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Threads" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Threads" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Threads" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Threads" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sequential" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2 Threads" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4 Threads" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="6 Threads" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="8 Threads" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="12 Threads" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Processes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +39,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -255,7 +255,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -270,13 +270,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -295,13 +295,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -310,7 +310,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -325,13 +325,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -340,7 +340,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -355,13 +355,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -385,13 +385,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -400,7 +400,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -415,13 +415,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -430,7 +430,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -445,13 +445,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -460,7 +460,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -475,13 +475,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -490,7 +490,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -505,13 +505,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -844,7 +844,7 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Sequential
-Average (ms)</t>
+Average (s)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -856,7 +856,7 @@
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>2 Threads
-Average (ms)</t>
+Average (s)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -868,7 +868,7 @@
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>4 Threads
-Average (ms)</t>
+Average (s)</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -880,7 +880,7 @@
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>6 Threads
-Average (ms)</t>
+Average (s)</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -892,7 +892,7 @@
       <c r="J2" s="3" t="inlineStr">
         <is>
           <t>8 Threads
-Average (ms)</t>
+Average (s)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>12 Threads
-Average (ms)</t>
+Average (s)</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -916,7 +916,7 @@
       <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Processes
-Average (ms)</t>
+Average (s)</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Average (ms)</t>
+          <t>Average (s)</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -1315,7 +1315,7 @@
         <v>0.021</v>
       </c>
       <c r="L3" s="10">
-        <f>IFERROR(AVERAGE(B3:K3), "N/A")</f>
+        <f>IFERROR(AVERAGE(B3:K3),"N/A")</f>
         <v/>
       </c>
       <c r="M3" s="11" t="n">
@@ -1359,7 +1359,7 @@
         <v>0.168</v>
       </c>
       <c r="L4" s="10">
-        <f>IFERROR(AVERAGE(B4:K4), "N/A")</f>
+        <f>IFERROR(AVERAGE(B4:K4),"N/A")</f>
         <v/>
       </c>
       <c r="M4" s="11" t="n">
@@ -1403,7 +1403,7 @@
         <v>1.34</v>
       </c>
       <c r="L5" s="10">
-        <f>IFERROR(AVERAGE(B5:K5), "N/A")</f>
+        <f>IFERROR(AVERAGE(B5:K5),"N/A")</f>
         <v/>
       </c>
       <c r="M5" s="11" t="n">
@@ -1447,7 +1447,7 @@
         <v>11.052</v>
       </c>
       <c r="L6" s="10">
-        <f>IFERROR(AVERAGE(B6:K6), "N/A")</f>
+        <f>IFERROR(AVERAGE(B6:K6),"N/A")</f>
         <v/>
       </c>
       <c r="M6" s="11" t="n">
@@ -1491,7 +1491,7 @@
         <v>104.311</v>
       </c>
       <c r="L7" s="10">
-        <f>IFERROR(AVERAGE(B7:K7), "N/A")</f>
+        <f>IFERROR(AVERAGE(B7:K7),"N/A")</f>
         <v/>
       </c>
       <c r="M7" s="11" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Average (ms)</t>
+          <t>Average (s)</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -1642,7 +1642,7 @@
         <v>0.011</v>
       </c>
       <c r="L3" s="10">
-        <f>IFERROR(AVERAGE(B3:K3), "N/A")</f>
+        <f>IFERROR(AVERAGE(B3:K3),"N/A")</f>
         <v/>
       </c>
       <c r="M3" s="11" t="n">
@@ -1686,7 +1686,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="L4" s="10">
-        <f>IFERROR(AVERAGE(B4:K4), "N/A")</f>
+        <f>IFERROR(AVERAGE(B4:K4),"N/A")</f>
         <v/>
       </c>
       <c r="M4" s="11" t="n">
@@ -1730,7 +1730,7 @@
         <v>0.666</v>
       </c>
       <c r="L5" s="10">
-        <f>IFERROR(AVERAGE(B5:K5), "N/A")</f>
+        <f>IFERROR(AVERAGE(B5:K5),"N/A")</f>
         <v/>
       </c>
       <c r="M5" s="11" t="n">
@@ -1774,7 +1774,7 @@
         <v>5.393</v>
       </c>
       <c r="L6" s="10">
-        <f>IFERROR(AVERAGE(B6:K6), "N/A")</f>
+        <f>IFERROR(AVERAGE(B6:K6),"N/A")</f>
         <v/>
       </c>
       <c r="M6" s="11" t="n">
@@ -1818,7 +1818,7 @@
         <v>51.299</v>
       </c>
       <c r="L7" s="10">
-        <f>IFERROR(AVERAGE(B7:K7), "N/A")</f>
+        <f>IFERROR(AVERAGE(B7:K7),"N/A")</f>
         <v/>
       </c>
       <c r="M7" s="11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Average (ms)</t>
+          <t>Average (s)</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -1969,7 +1969,7 @@
         <v>0.005</v>
       </c>
       <c r="L3" s="10">
-        <f>IFERROR(AVERAGE(B3:K3), "N/A")</f>
+        <f>IFERROR(AVERAGE(B3:K3),"N/A")</f>
         <v/>
       </c>
       <c r="M3" s="11" t="n">
@@ -2013,7 +2013,7 @@
         <v>0.042</v>
       </c>
       <c r="L4" s="10">
-        <f>IFERROR(AVERAGE(B4:K4), "N/A")</f>
+        <f>IFERROR(AVERAGE(B4:K4),"N/A")</f>
         <v/>
       </c>
       <c r="M4" s="11" t="n">
@@ -2057,7 +2057,7 @@
         <v>0.339</v>
       </c>
       <c r="L5" s="10">
-        <f>IFERROR(AVERAGE(B5:K5), "N/A")</f>
+        <f>IFERROR(AVERAGE(B5:K5),"N/A")</f>
         <v/>
       </c>
       <c r="M5" s="11" t="n">
@@ -2101,7 +2101,7 @@
         <v>2.747</v>
       </c>
       <c r="L6" s="10">
-        <f>IFERROR(AVERAGE(B6:K6), "N/A")</f>
+        <f>IFERROR(AVERAGE(B6:K6),"N/A")</f>
         <v/>
       </c>
       <c r="M6" s="11" t="n">
@@ -2145,7 +2145,7 @@
         <v>25.034</v>
       </c>
       <c r="L7" s="10">
-        <f>IFERROR(AVERAGE(B7:K7), "N/A")</f>
+        <f>IFERROR(AVERAGE(B7:K7),"N/A")</f>
         <v/>
       </c>
       <c r="M7" s="11" t="n">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Average (ms)</t>
+          <t>Average (s)</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -2296,7 +2296,7 @@
         <v>0.007</v>
       </c>
       <c r="L3" s="10">
-        <f>IFERROR(AVERAGE(B3:K3), "N/A")</f>
+        <f>IFERROR(AVERAGE(B3:K3),"N/A")</f>
         <v/>
       </c>
       <c r="M3" s="11" t="n">
@@ -2340,7 +2340,7 @@
         <v>0.029</v>
       </c>
       <c r="L4" s="10">
-        <f>IFERROR(AVERAGE(B4:K4), "N/A")</f>
+        <f>IFERROR(AVERAGE(B4:K4),"N/A")</f>
         <v/>
       </c>
       <c r="M4" s="11" t="n">
@@ -2384,7 +2384,7 @@
         <v>0.225</v>
       </c>
       <c r="L5" s="10">
-        <f>IFERROR(AVERAGE(B5:K5), "N/A")</f>
+        <f>IFERROR(AVERAGE(B5:K5),"N/A")</f>
         <v/>
       </c>
       <c r="M5" s="11" t="n">
@@ -2428,7 +2428,7 @@
         <v>1.847</v>
       </c>
       <c r="L6" s="10">
-        <f>IFERROR(AVERAGE(B6:K6), "N/A")</f>
+        <f>IFERROR(AVERAGE(B6:K6),"N/A")</f>
         <v/>
       </c>
       <c r="M6" s="11" t="n">
@@ -2472,7 +2472,7 @@
         <v>17.097</v>
       </c>
       <c r="L7" s="10">
-        <f>IFERROR(AVERAGE(B7:K7), "N/A")</f>
+        <f>IFERROR(AVERAGE(B7:K7),"N/A")</f>
         <v/>
       </c>
       <c r="M7" s="11" t="n">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Average (ms)</t>
+          <t>Average (s)</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -2623,7 +2623,7 @@
         <v>0.005</v>
       </c>
       <c r="L3" s="10">
-        <f>IFERROR(AVERAGE(B3:K3), "N/A")</f>
+        <f>IFERROR(AVERAGE(B3:K3),"N/A")</f>
         <v/>
       </c>
       <c r="M3" s="11" t="n">
@@ -2667,7 +2667,7 @@
         <v>0.042</v>
       </c>
       <c r="L4" s="10">
-        <f>IFERROR(AVERAGE(B4:K4), "N/A")</f>
+        <f>IFERROR(AVERAGE(B4:K4),"N/A")</f>
         <v/>
       </c>
       <c r="M4" s="11" t="n">
@@ -2711,7 +2711,7 @@
         <v>0.333</v>
       </c>
       <c r="L5" s="10">
-        <f>IFERROR(AVERAGE(B5:K5), "N/A")</f>
+        <f>IFERROR(AVERAGE(B5:K5),"N/A")</f>
         <v/>
       </c>
       <c r="M5" s="11" t="n">
@@ -2755,7 +2755,7 @@
         <v>2.688</v>
       </c>
       <c r="L6" s="10">
-        <f>IFERROR(AVERAGE(B6:K6), "N/A")</f>
+        <f>IFERROR(AVERAGE(B6:K6),"N/A")</f>
         <v/>
       </c>
       <c r="M6" s="11" t="n">
@@ -2799,7 +2799,7 @@
         <v>25.192</v>
       </c>
       <c r="L7" s="10">
-        <f>IFERROR(AVERAGE(B7:K7), "N/A")</f>
+        <f>IFERROR(AVERAGE(B7:K7),"N/A")</f>
         <v/>
       </c>
       <c r="M7" s="11" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Average (ms)</t>
+          <t>Average (s)</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -2950,7 +2950,7 @@
         <v>0.004</v>
       </c>
       <c r="L3" s="10">
-        <f>IFERROR(AVERAGE(B3:K3), "N/A")</f>
+        <f>IFERROR(AVERAGE(B3:K3),"N/A")</f>
         <v/>
       </c>
       <c r="M3" s="11" t="n">
@@ -2994,7 +2994,7 @@
         <v>0.03</v>
       </c>
       <c r="L4" s="10">
-        <f>IFERROR(AVERAGE(B4:K4), "N/A")</f>
+        <f>IFERROR(AVERAGE(B4:K4),"N/A")</f>
         <v/>
       </c>
       <c r="M4" s="11" t="n">
@@ -3038,7 +3038,7 @@
         <v>0.226</v>
       </c>
       <c r="L5" s="10">
-        <f>IFERROR(AVERAGE(B5:K5), "N/A")</f>
+        <f>IFERROR(AVERAGE(B5:K5),"N/A")</f>
         <v/>
       </c>
       <c r="M5" s="11" t="n">
@@ -3082,7 +3082,7 @@
         <v>1.846</v>
       </c>
       <c r="L6" s="10">
-        <f>IFERROR(AVERAGE(B6:K6), "N/A")</f>
+        <f>IFERROR(AVERAGE(B6:K6),"N/A")</f>
         <v/>
       </c>
       <c r="M6" s="11" t="n">
@@ -3126,7 +3126,7 @@
         <v>16.873</v>
       </c>
       <c r="L7" s="10">
-        <f>IFERROR(AVERAGE(B7:K7), "N/A")</f>
+        <f>IFERROR(AVERAGE(B7:K7),"N/A")</f>
         <v/>
       </c>
       <c r="M7" s="11" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Average (ms)</t>
+          <t>Average (s)</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -3277,7 +3277,7 @@
         <v>0.004</v>
       </c>
       <c r="L3" s="10">
-        <f>IFERROR(AVERAGE(B3:K3), "N/A")</f>
+        <f>IFERROR(AVERAGE(B3:K3),"N/A")</f>
         <v/>
       </c>
       <c r="M3" s="11" t="n">
@@ -3321,7 +3321,7 @@
         <v>0.029</v>
       </c>
       <c r="L4" s="10">
-        <f>IFERROR(AVERAGE(B4:K4), "N/A")</f>
+        <f>IFERROR(AVERAGE(B4:K4),"N/A")</f>
         <v/>
       </c>
       <c r="M4" s="11" t="n">
@@ -3365,7 +3365,7 @@
         <v>0.227</v>
       </c>
       <c r="L5" s="10">
-        <f>IFERROR(AVERAGE(B5:K5), "N/A")</f>
+        <f>IFERROR(AVERAGE(B5:K5),"N/A")</f>
         <v/>
       </c>
       <c r="M5" s="11" t="n">
@@ -3409,7 +3409,7 @@
         <v>1.9</v>
       </c>
       <c r="L6" s="10">
-        <f>IFERROR(AVERAGE(B6:K6), "N/A")</f>
+        <f>IFERROR(AVERAGE(B6:K6),"N/A")</f>
         <v/>
       </c>
       <c r="M6" s="11" t="n">
@@ -3453,7 +3453,7 @@
         <v>17.056</v>
       </c>
       <c r="L7" s="10">
-        <f>IFERROR(AVERAGE(B7:K7), "N/A")</f>
+        <f>IFERROR(AVERAGE(B7:K7),"N/A")</f>
         <v/>
       </c>
       <c r="M7" s="11" t="n">
